--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Myburgh Swiegers\Projects\Codex_GDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABAC343-A436-416B-A05E-812030FE4DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0CD56-CAC4-4BC2-AB7E-7381AD21C78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="453">
   <si>
     <t>2024/25</t>
   </si>
@@ -1393,6 +1393,9 @@
   </si>
   <si>
     <t>13/06 - 19/06/2026</t>
+  </si>
+  <si>
+    <t>20/06 - 26/06/2026</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1406,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1452,12 +1455,6 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1606,7 +1603,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1657,12 +1654,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1946,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L435"/>
+  <dimension ref="A1:L436"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10409,16 +10400,16 @@
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="37" t="s">
+      <c r="C420" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="34">
+      <c r="D420" s="6">
         <v>8059</v>
       </c>
-      <c r="E420" s="34">
+      <c r="E420" s="6">
         <v>742</v>
       </c>
-      <c r="F420" s="34">
+      <c r="F420" s="6">
         <v>8801</v>
       </c>
     </row>
@@ -10429,16 +10420,16 @@
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="38" t="s">
+      <c r="C421" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="35">
+      <c r="D421" s="8">
         <v>22734</v>
       </c>
-      <c r="E421" s="35">
+      <c r="E421" s="8">
         <v>922</v>
       </c>
-      <c r="F421" s="35">
+      <c r="F421" s="8">
         <v>23656</v>
       </c>
     </row>
@@ -10449,16 +10440,16 @@
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="38" t="s">
+      <c r="C422" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="35">
+      <c r="D422" s="8">
         <v>26484</v>
       </c>
-      <c r="E422" s="35">
+      <c r="E422" s="8">
         <v>3923</v>
       </c>
-      <c r="F422" s="35">
+      <c r="F422" s="8">
         <v>30407</v>
       </c>
     </row>
@@ -10469,16 +10460,16 @@
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="38" t="s">
+      <c r="C423" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="35">
+      <c r="D423" s="8">
         <v>17047</v>
       </c>
-      <c r="E423" s="35">
+      <c r="E423" s="8">
         <v>2351</v>
       </c>
-      <c r="F423" s="35">
+      <c r="F423" s="8">
         <v>19398</v>
       </c>
     </row>
@@ -10489,16 +10480,16 @@
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="38" t="s">
+      <c r="C424" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="35">
+      <c r="D424" s="8">
         <v>39182</v>
       </c>
-      <c r="E424" s="35">
+      <c r="E424" s="8">
         <v>2818</v>
       </c>
-      <c r="F424" s="35">
+      <c r="F424" s="8">
         <v>42000</v>
       </c>
     </row>
@@ -10509,16 +10500,16 @@
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="38" t="s">
+      <c r="C425" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="35">
+      <c r="D425" s="8">
         <v>75766</v>
       </c>
-      <c r="E425" s="35">
+      <c r="E425" s="8">
         <v>3686</v>
       </c>
-      <c r="F425" s="35">
+      <c r="F425" s="8">
         <v>79452</v>
       </c>
     </row>
@@ -10529,16 +10520,16 @@
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="38" t="s">
+      <c r="C426" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="35">
+      <c r="D426" s="8">
         <v>56615</v>
       </c>
-      <c r="E426" s="35">
+      <c r="E426" s="8">
         <v>631</v>
       </c>
-      <c r="F426" s="35">
+      <c r="F426" s="8">
         <v>57246</v>
       </c>
     </row>
@@ -10549,16 +10540,16 @@
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="38" t="s">
+      <c r="C427" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="35">
+      <c r="D427" s="8">
         <v>33342</v>
       </c>
-      <c r="E427" s="35">
+      <c r="E427" s="8">
         <v>2446</v>
       </c>
-      <c r="F427" s="35">
+      <c r="F427" s="8">
         <v>35788</v>
       </c>
     </row>
@@ -10569,17 +10560,17 @@
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="38" t="s">
+      <c r="C428" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="35">
+      <c r="D428" s="8">
         <v>55113</v>
       </c>
-      <c r="E428" s="35">
-        <v>255</v>
-      </c>
-      <c r="F428" s="35">
-        <v>55368</v>
+      <c r="E428" s="8">
+        <v>1637</v>
+      </c>
+      <c r="F428" s="8">
+        <v>56750</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -10589,17 +10580,17 @@
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="38" t="s">
+      <c r="C429" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="35">
+      <c r="D429" s="8">
         <v>44476</v>
       </c>
-      <c r="E429" s="35">
-        <v>-3</v>
-      </c>
-      <c r="F429" s="35">
-        <v>44473</v>
+      <c r="E429" s="8">
+        <v>-252</v>
+      </c>
+      <c r="F429" s="8">
+        <v>44224</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -10609,17 +10600,17 @@
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="38" t="s">
+      <c r="C430" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="35">
+      <c r="D430" s="8">
         <v>99689</v>
       </c>
-      <c r="E430" s="35">
-        <v>377</v>
-      </c>
-      <c r="F430" s="35">
-        <v>100066</v>
+      <c r="E430" s="8">
+        <v>1383</v>
+      </c>
+      <c r="F430" s="8">
+        <v>101072</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -10629,17 +10620,17 @@
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="38" t="s">
+      <c r="C431" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="35">
+      <c r="D431" s="8">
         <v>83530</v>
       </c>
-      <c r="E431" s="35">
-        <v>1447</v>
-      </c>
-      <c r="F431" s="35">
-        <v>84977</v>
+      <c r="E431" s="8">
+        <v>2259</v>
+      </c>
+      <c r="F431" s="8">
+        <v>85789</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -10649,17 +10640,17 @@
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="38" t="s">
+      <c r="C432" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="35">
+      <c r="D432" s="8">
         <v>59752</v>
       </c>
-      <c r="E432" s="35">
-        <v>104</v>
-      </c>
-      <c r="F432" s="35">
-        <v>59856</v>
+      <c r="E432" s="8">
+        <v>703</v>
+      </c>
+      <c r="F432" s="8">
+        <v>60455</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -10669,16 +10660,16 @@
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="38" t="s">
+      <c r="C433" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="35">
+      <c r="D433" s="8">
         <v>40427</v>
       </c>
-      <c r="E433" s="35">
-        <v>0</v>
-      </c>
-      <c r="F433" s="35">
+      <c r="E433" s="8">
+        <v>0</v>
+      </c>
+      <c r="F433" s="8">
         <v>40427</v>
       </c>
     </row>
@@ -10689,16 +10680,16 @@
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="38" t="s">
+      <c r="C434" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="35">
+      <c r="D434" s="8">
         <v>36123</v>
       </c>
-      <c r="E434" s="35">
-        <v>0</v>
-      </c>
-      <c r="F434" s="35">
+      <c r="E434" s="8">
+        <v>0</v>
+      </c>
+      <c r="F434" s="8">
         <v>36123</v>
       </c>
     </row>
@@ -10709,17 +10700,37 @@
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="39" t="s">
+      <c r="C435" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="36">
+      <c r="D435" s="8">
         <v>28792</v>
       </c>
-      <c r="E435" s="36">
-        <v>0</v>
-      </c>
-      <c r="F435" s="36">
+      <c r="E435" s="8">
+        <v>0</v>
+      </c>
+      <c r="F435" s="8">
         <v>28792</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A436" s="2">
+        <v>17</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D436" s="1">
+        <v>10316</v>
+      </c>
+      <c r="E436" s="1">
+        <v>0</v>
+      </c>
+      <c r="F436" s="1">
+        <v>10316</v>
       </c>
     </row>
   </sheetData>
@@ -10730,7 +10741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L435"/>
+  <dimension ref="A1:L436"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19239,10 +19250,10 @@
         <v>20480</v>
       </c>
       <c r="E422" s="8">
-        <v>1456</v>
+        <v>1526</v>
       </c>
       <c r="F422" s="8">
-        <v>21936</v>
+        <v>22006</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -19259,10 +19270,10 @@
         <v>14216</v>
       </c>
       <c r="E423" s="8">
-        <v>1720</v>
+        <v>1821</v>
       </c>
       <c r="F423" s="8">
-        <v>15936</v>
+        <v>16037</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -19279,10 +19290,10 @@
         <v>58007</v>
       </c>
       <c r="E424" s="8">
-        <v>5505</v>
+        <v>5603</v>
       </c>
       <c r="F424" s="8">
-        <v>63512</v>
+        <v>63610</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -19299,10 +19310,10 @@
         <v>134411</v>
       </c>
       <c r="E425" s="8">
-        <v>13591</v>
+        <v>13879</v>
       </c>
       <c r="F425" s="8">
-        <v>148002</v>
+        <v>148290</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -19319,10 +19330,10 @@
         <v>99724</v>
       </c>
       <c r="E426" s="8">
-        <v>-1215</v>
+        <v>-1250</v>
       </c>
       <c r="F426" s="8">
-        <v>98509</v>
+        <v>98474</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -19339,10 +19350,10 @@
         <v>64774</v>
       </c>
       <c r="E427" s="8">
-        <v>7974</v>
+        <v>11131</v>
       </c>
       <c r="F427" s="8">
-        <v>72748</v>
+        <v>75905</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -19359,10 +19370,10 @@
         <v>137672</v>
       </c>
       <c r="E428" s="8">
-        <v>1957</v>
+        <v>5570</v>
       </c>
       <c r="F428" s="8">
-        <v>139629</v>
+        <v>143242</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -19379,10 +19390,10 @@
         <v>154371</v>
       </c>
       <c r="E429" s="8">
-        <v>406</v>
+        <v>687</v>
       </c>
       <c r="F429" s="8">
-        <v>154777</v>
+        <v>155058</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -19399,10 +19410,10 @@
         <v>588453</v>
       </c>
       <c r="E430" s="8">
-        <v>7993</v>
+        <v>11507</v>
       </c>
       <c r="F430" s="8">
-        <v>596446</v>
+        <v>599960</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -19419,10 +19430,10 @@
         <v>561432</v>
       </c>
       <c r="E431" s="8">
-        <v>6842</v>
+        <v>9166</v>
       </c>
       <c r="F431" s="8">
-        <v>568274</v>
+        <v>570598</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -19439,10 +19450,10 @@
         <v>370449</v>
       </c>
       <c r="E432" s="8">
-        <v>19342</v>
+        <v>25159</v>
       </c>
       <c r="F432" s="8">
-        <v>389791</v>
+        <v>395608</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -19492,17 +19503,37 @@
       <c r="B435" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="2" t="s">
+      <c r="C435" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="1">
+      <c r="D435" s="8">
         <v>62064</v>
       </c>
-      <c r="E435" s="1">
-        <v>0</v>
-      </c>
-      <c r="F435" s="1">
+      <c r="E435" s="8">
+        <v>0</v>
+      </c>
+      <c r="F435" s="8">
         <v>62064</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A436" s="2">
+        <v>17</v>
+      </c>
+      <c r="B436" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D436" s="1">
+        <v>26534</v>
+      </c>
+      <c r="E436" s="1">
+        <v>0</v>
+      </c>
+      <c r="F436" s="1">
+        <v>26534</v>
       </c>
     </row>
   </sheetData>
@@ -19523,6 +19554,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -19749,15 +19789,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
@@ -19770,6 +19801,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19786,12 +19825,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Myburgh Swiegers\Projects\Codex_GDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0CD56-CAC4-4BC2-AB7E-7381AD21C78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C462D42-B7C0-4D76-A2AB-4F85A7DC259F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="454">
   <si>
     <t>2024/25</t>
   </si>
@@ -1396,6 +1396,9 @@
   </si>
   <si>
     <t>20/06 - 26/06/2026</t>
+  </si>
+  <si>
+    <t>27/06 - 03/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1409,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1462,6 +1465,11 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1489,7 +1497,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1596,6 +1604,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0A0101"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0A0101"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FF0A0101"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1603,7 +1637,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1652,8 +1686,17 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1937,7 +1980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L436"/>
+  <dimension ref="A1:L437"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10400,16 +10443,16 @@
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="5" t="s">
+      <c r="C420" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="6">
+      <c r="D420" s="34">
         <v>8059</v>
       </c>
-      <c r="E420" s="6">
+      <c r="E420" s="34">
         <v>742</v>
       </c>
-      <c r="F420" s="6">
+      <c r="F420" s="34">
         <v>8801</v>
       </c>
     </row>
@@ -10420,16 +10463,16 @@
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="7" t="s">
+      <c r="C421" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="8">
+      <c r="D421" s="35">
         <v>22734</v>
       </c>
-      <c r="E421" s="8">
+      <c r="E421" s="35">
         <v>922</v>
       </c>
-      <c r="F421" s="8">
+      <c r="F421" s="35">
         <v>23656</v>
       </c>
     </row>
@@ -10440,16 +10483,16 @@
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="7" t="s">
+      <c r="C422" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="8">
+      <c r="D422" s="35">
         <v>26484</v>
       </c>
-      <c r="E422" s="8">
+      <c r="E422" s="35">
         <v>3923</v>
       </c>
-      <c r="F422" s="8">
+      <c r="F422" s="35">
         <v>30407</v>
       </c>
     </row>
@@ -10460,16 +10503,16 @@
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="7" t="s">
+      <c r="C423" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="8">
+      <c r="D423" s="35">
         <v>17047</v>
       </c>
-      <c r="E423" s="8">
+      <c r="E423" s="35">
         <v>2351</v>
       </c>
-      <c r="F423" s="8">
+      <c r="F423" s="35">
         <v>19398</v>
       </c>
     </row>
@@ -10480,16 +10523,16 @@
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="7" t="s">
+      <c r="C424" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="8">
+      <c r="D424" s="35">
         <v>39182</v>
       </c>
-      <c r="E424" s="8">
+      <c r="E424" s="35">
         <v>2818</v>
       </c>
-      <c r="F424" s="8">
+      <c r="F424" s="35">
         <v>42000</v>
       </c>
     </row>
@@ -10500,16 +10543,16 @@
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="7" t="s">
+      <c r="C425" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="8">
+      <c r="D425" s="35">
         <v>75766</v>
       </c>
-      <c r="E425" s="8">
+      <c r="E425" s="35">
         <v>3686</v>
       </c>
-      <c r="F425" s="8">
+      <c r="F425" s="35">
         <v>79452</v>
       </c>
     </row>
@@ -10520,16 +10563,16 @@
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="7" t="s">
+      <c r="C426" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="8">
+      <c r="D426" s="35">
         <v>56615</v>
       </c>
-      <c r="E426" s="8">
+      <c r="E426" s="35">
         <v>631</v>
       </c>
-      <c r="F426" s="8">
+      <c r="F426" s="35">
         <v>57246</v>
       </c>
     </row>
@@ -10540,16 +10583,16 @@
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="7" t="s">
+      <c r="C427" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="8">
+      <c r="D427" s="35">
         <v>33342</v>
       </c>
-      <c r="E427" s="8">
+      <c r="E427" s="35">
         <v>2446</v>
       </c>
-      <c r="F427" s="8">
+      <c r="F427" s="35">
         <v>35788</v>
       </c>
     </row>
@@ -10560,16 +10603,16 @@
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="7" t="s">
+      <c r="C428" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="8">
+      <c r="D428" s="35">
         <v>55113</v>
       </c>
-      <c r="E428" s="8">
+      <c r="E428" s="35">
         <v>1637</v>
       </c>
-      <c r="F428" s="8">
+      <c r="F428" s="35">
         <v>56750</v>
       </c>
     </row>
@@ -10580,16 +10623,16 @@
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="7" t="s">
+      <c r="C429" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="8">
+      <c r="D429" s="35">
         <v>44476</v>
       </c>
-      <c r="E429" s="8">
+      <c r="E429" s="35">
         <v>-252</v>
       </c>
-      <c r="F429" s="8">
+      <c r="F429" s="35">
         <v>44224</v>
       </c>
     </row>
@@ -10600,16 +10643,16 @@
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="7" t="s">
+      <c r="C430" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="8">
+      <c r="D430" s="35">
         <v>99689</v>
       </c>
-      <c r="E430" s="8">
+      <c r="E430" s="35">
         <v>1383</v>
       </c>
-      <c r="F430" s="8">
+      <c r="F430" s="35">
         <v>101072</v>
       </c>
     </row>
@@ -10620,16 +10663,16 @@
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="7" t="s">
+      <c r="C431" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="8">
+      <c r="D431" s="35">
         <v>83530</v>
       </c>
-      <c r="E431" s="8">
+      <c r="E431" s="35">
         <v>2259</v>
       </c>
-      <c r="F431" s="8">
+      <c r="F431" s="35">
         <v>85789</v>
       </c>
     </row>
@@ -10640,16 +10683,16 @@
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="7" t="s">
+      <c r="C432" s="38" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="8">
+      <c r="D432" s="35">
         <v>59752</v>
       </c>
-      <c r="E432" s="8">
+      <c r="E432" s="35">
         <v>703</v>
       </c>
-      <c r="F432" s="8">
+      <c r="F432" s="35">
         <v>60455</v>
       </c>
     </row>
@@ -10660,16 +10703,16 @@
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="7" t="s">
+      <c r="C433" s="38" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="8">
+      <c r="D433" s="35">
         <v>40427</v>
       </c>
-      <c r="E433" s="8">
-        <v>0</v>
-      </c>
-      <c r="F433" s="8">
+      <c r="E433" s="35">
+        <v>0</v>
+      </c>
+      <c r="F433" s="35">
         <v>40427</v>
       </c>
     </row>
@@ -10680,16 +10723,16 @@
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="7" t="s">
+      <c r="C434" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="8">
+      <c r="D434" s="35">
         <v>36123</v>
       </c>
-      <c r="E434" s="8">
-        <v>0</v>
-      </c>
-      <c r="F434" s="8">
+      <c r="E434" s="35">
+        <v>0</v>
+      </c>
+      <c r="F434" s="35">
         <v>36123</v>
       </c>
     </row>
@@ -10700,37 +10743,57 @@
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="7" t="s">
+      <c r="C435" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="8">
+      <c r="D435" s="35">
         <v>28792</v>
       </c>
-      <c r="E435" s="8">
-        <v>0</v>
-      </c>
-      <c r="F435" s="8">
+      <c r="E435" s="35">
+        <v>0</v>
+      </c>
+      <c r="F435" s="35">
         <v>28792</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A436" s="2">
+      <c r="A436" s="32">
         <v>17</v>
       </c>
-      <c r="B436" s="3" t="s">
+      <c r="B436" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="2" t="s">
+      <c r="C436" s="38" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="1">
+      <c r="D436" s="35">
         <v>10316</v>
       </c>
-      <c r="E436" s="1">
-        <v>0</v>
-      </c>
-      <c r="F436" s="1">
-        <v>10316</v>
+      <c r="E436" s="35">
+        <v>1198</v>
+      </c>
+      <c r="F436" s="35">
+        <v>11514</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A437" s="18">
+        <v>18</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C437" s="39" t="s">
+        <v>453</v>
+      </c>
+      <c r="D437" s="36">
+        <v>12812</v>
+      </c>
+      <c r="E437" s="36">
+        <v>0</v>
+      </c>
+      <c r="F437" s="36">
+        <v>12812</v>
       </c>
     </row>
   </sheetData>
@@ -10741,7 +10804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L436"/>
+  <dimension ref="A1:L437"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19183,27 +19246,27 @@
       <c r="B419" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C419" s="32" t="s">
+      <c r="C419" s="40" t="s">
         <v>444</v>
       </c>
-      <c r="D419" s="33">
+      <c r="D419" s="41">
         <v>3477</v>
       </c>
-      <c r="E419" s="33">
+      <c r="E419" s="41">
         <v>763</v>
       </c>
-      <c r="F419" s="33">
+      <c r="F419" s="41">
         <v>4240</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A420" s="30">
+      <c r="A420" s="18">
         <v>1</v>
       </c>
-      <c r="B420" s="26" t="s">
+      <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="5" t="s">
+      <c r="C420" s="42" t="s">
         <v>9</v>
       </c>
       <c r="D420" s="6">
@@ -19217,13 +19280,13 @@
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A421" s="7">
+      <c r="A421" s="18">
         <v>2</v>
       </c>
-      <c r="B421" s="26" t="s">
+      <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="7" t="s">
+      <c r="C421" s="42" t="s">
         <v>10</v>
       </c>
       <c r="D421" s="8">
@@ -19237,13 +19300,13 @@
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A422" s="7">
+      <c r="A422" s="18">
         <v>3</v>
       </c>
-      <c r="B422" s="26" t="s">
+      <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="7" t="s">
+      <c r="C422" s="42" t="s">
         <v>11</v>
       </c>
       <c r="D422" s="8">
@@ -19257,13 +19320,13 @@
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A423" s="7">
+      <c r="A423" s="18">
         <v>4</v>
       </c>
-      <c r="B423" s="26" t="s">
+      <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="7" t="s">
+      <c r="C423" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D423" s="8">
@@ -19277,13 +19340,13 @@
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A424" s="7">
+      <c r="A424" s="18">
         <v>5</v>
       </c>
-      <c r="B424" s="26" t="s">
+      <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="7" t="s">
+      <c r="C424" s="42" t="s">
         <v>13</v>
       </c>
       <c r="D424" s="8">
@@ -19297,13 +19360,13 @@
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A425" s="7">
+      <c r="A425" s="18">
         <v>6</v>
       </c>
-      <c r="B425" s="26" t="s">
+      <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="7" t="s">
+      <c r="C425" s="42" t="s">
         <v>14</v>
       </c>
       <c r="D425" s="8">
@@ -19317,13 +19380,13 @@
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A426" s="7">
+      <c r="A426" s="18">
         <v>7</v>
       </c>
-      <c r="B426" s="26" t="s">
+      <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="7" t="s">
+      <c r="C426" s="42" t="s">
         <v>15</v>
       </c>
       <c r="D426" s="8">
@@ -19337,13 +19400,13 @@
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A427" s="7">
+      <c r="A427" s="18">
         <v>8</v>
       </c>
-      <c r="B427" s="26" t="s">
+      <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="7" t="s">
+      <c r="C427" s="42" t="s">
         <v>16</v>
       </c>
       <c r="D427" s="8">
@@ -19357,13 +19420,13 @@
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A428" s="7">
+      <c r="A428" s="18">
         <v>9</v>
       </c>
-      <c r="B428" s="26" t="s">
+      <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="7" t="s">
+      <c r="C428" s="42" t="s">
         <v>17</v>
       </c>
       <c r="D428" s="8">
@@ -19377,13 +19440,13 @@
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A429" s="7">
+      <c r="A429" s="18">
         <v>10</v>
       </c>
-      <c r="B429" s="26" t="s">
+      <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="7" t="s">
+      <c r="C429" s="42" t="s">
         <v>18</v>
       </c>
       <c r="D429" s="8">
@@ -19397,13 +19460,13 @@
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A430" s="7">
+      <c r="A430" s="18">
         <v>11</v>
       </c>
-      <c r="B430" s="26" t="s">
+      <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="7" t="s">
+      <c r="C430" s="42" t="s">
         <v>19</v>
       </c>
       <c r="D430" s="8">
@@ -19417,13 +19480,13 @@
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A431" s="7">
+      <c r="A431" s="18">
         <v>12</v>
       </c>
-      <c r="B431" s="26" t="s">
+      <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="7" t="s">
+      <c r="C431" s="42" t="s">
         <v>20</v>
       </c>
       <c r="D431" s="8">
@@ -19437,13 +19500,13 @@
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A432" s="7">
+      <c r="A432" s="18">
         <v>13</v>
       </c>
-      <c r="B432" s="26" t="s">
+      <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="7" t="s">
+      <c r="C432" s="42" t="s">
         <v>448</v>
       </c>
       <c r="D432" s="8">
@@ -19457,13 +19520,13 @@
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A433" s="7">
+      <c r="A433" s="18">
         <v>14</v>
       </c>
-      <c r="B433" s="26" t="s">
+      <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="7" t="s">
+      <c r="C433" s="42" t="s">
         <v>449</v>
       </c>
       <c r="D433" s="8">
@@ -19477,13 +19540,13 @@
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A434" s="2">
+      <c r="A434" s="18">
         <v>15</v>
       </c>
-      <c r="B434" s="26" t="s">
+      <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="7" t="s">
+      <c r="C434" s="42" t="s">
         <v>450</v>
       </c>
       <c r="D434" s="8">
@@ -19497,13 +19560,13 @@
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A435" s="2">
+      <c r="A435" s="18">
         <v>16</v>
       </c>
-      <c r="B435" s="26" t="s">
+      <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="7" t="s">
+      <c r="C435" s="42" t="s">
         <v>451</v>
       </c>
       <c r="D435" s="8">
@@ -19517,23 +19580,43 @@
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A436" s="2">
+      <c r="A436" s="18">
         <v>17</v>
       </c>
-      <c r="B436" s="26" t="s">
+      <c r="B436" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="2" t="s">
+      <c r="C436" s="42" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="1">
+      <c r="D436" s="8">
         <v>26534</v>
       </c>
-      <c r="E436" s="1">
-        <v>0</v>
-      </c>
-      <c r="F436" s="1">
-        <v>26534</v>
+      <c r="E436" s="8">
+        <v>845</v>
+      </c>
+      <c r="F436" s="8">
+        <v>27379</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A437" s="3">
+        <v>18</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C437" s="42" t="s">
+        <v>453</v>
+      </c>
+      <c r="D437" s="1">
+        <v>19714</v>
+      </c>
+      <c r="E437" s="1">
+        <v>0</v>
+      </c>
+      <c r="F437" s="1">
+        <v>19714</v>
       </c>
     </row>
   </sheetData>
@@ -19543,6 +19626,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
@@ -19551,15 +19643,6 @@
     <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19790,20 +19873,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
     <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Myburgh Swiegers\Projects\Codex_GDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C462D42-B7C0-4D76-A2AB-4F85A7DC259F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583AF3BC-595B-4404-B96B-116C0E939D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="455">
   <si>
     <t>2024/25</t>
   </si>
@@ -1399,6 +1399,9 @@
   </si>
   <si>
     <t>27/06 - 03/07/2026</t>
+  </si>
+  <si>
+    <t>04/07 - 10/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1412,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1464,11 +1467,6 @@
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Narrow"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1637,7 +1635,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1688,15 +1686,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1980,7 +1971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L437"/>
+  <dimension ref="A1:L438"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10443,16 +10434,16 @@
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="37" t="s">
+      <c r="C420" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="34">
+      <c r="D420" s="6">
         <v>8059</v>
       </c>
-      <c r="E420" s="34">
+      <c r="E420" s="6">
         <v>742</v>
       </c>
-      <c r="F420" s="34">
+      <c r="F420" s="6">
         <v>8801</v>
       </c>
     </row>
@@ -10463,16 +10454,16 @@
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="38" t="s">
+      <c r="C421" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="35">
+      <c r="D421" s="8">
         <v>22734</v>
       </c>
-      <c r="E421" s="35">
+      <c r="E421" s="8">
         <v>922</v>
       </c>
-      <c r="F421" s="35">
+      <c r="F421" s="8">
         <v>23656</v>
       </c>
     </row>
@@ -10483,16 +10474,16 @@
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="38" t="s">
+      <c r="C422" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="35">
+      <c r="D422" s="8">
         <v>26484</v>
       </c>
-      <c r="E422" s="35">
+      <c r="E422" s="8">
         <v>3923</v>
       </c>
-      <c r="F422" s="35">
+      <c r="F422" s="8">
         <v>30407</v>
       </c>
     </row>
@@ -10503,16 +10494,16 @@
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="38" t="s">
+      <c r="C423" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="35">
+      <c r="D423" s="8">
         <v>17047</v>
       </c>
-      <c r="E423" s="35">
+      <c r="E423" s="8">
         <v>2351</v>
       </c>
-      <c r="F423" s="35">
+      <c r="F423" s="8">
         <v>19398</v>
       </c>
     </row>
@@ -10523,16 +10514,16 @@
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="38" t="s">
+      <c r="C424" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="35">
+      <c r="D424" s="8">
         <v>39182</v>
       </c>
-      <c r="E424" s="35">
+      <c r="E424" s="8">
         <v>2818</v>
       </c>
-      <c r="F424" s="35">
+      <c r="F424" s="8">
         <v>42000</v>
       </c>
     </row>
@@ -10543,16 +10534,16 @@
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="38" t="s">
+      <c r="C425" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="35">
+      <c r="D425" s="8">
         <v>75766</v>
       </c>
-      <c r="E425" s="35">
+      <c r="E425" s="8">
         <v>3686</v>
       </c>
-      <c r="F425" s="35">
+      <c r="F425" s="8">
         <v>79452</v>
       </c>
     </row>
@@ -10563,16 +10554,16 @@
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="38" t="s">
+      <c r="C426" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="35">
+      <c r="D426" s="8">
         <v>56615</v>
       </c>
-      <c r="E426" s="35">
+      <c r="E426" s="8">
         <v>631</v>
       </c>
-      <c r="F426" s="35">
+      <c r="F426" s="8">
         <v>57246</v>
       </c>
     </row>
@@ -10583,16 +10574,16 @@
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="38" t="s">
+      <c r="C427" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="35">
+      <c r="D427" s="8">
         <v>33342</v>
       </c>
-      <c r="E427" s="35">
+      <c r="E427" s="8">
         <v>2446</v>
       </c>
-      <c r="F427" s="35">
+      <c r="F427" s="8">
         <v>35788</v>
       </c>
     </row>
@@ -10603,16 +10594,16 @@
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="38" t="s">
+      <c r="C428" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="35">
+      <c r="D428" s="8">
         <v>55113</v>
       </c>
-      <c r="E428" s="35">
+      <c r="E428" s="8">
         <v>1637</v>
       </c>
-      <c r="F428" s="35">
+      <c r="F428" s="8">
         <v>56750</v>
       </c>
     </row>
@@ -10623,16 +10614,16 @@
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="38" t="s">
+      <c r="C429" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="35">
+      <c r="D429" s="8">
         <v>44476</v>
       </c>
-      <c r="E429" s="35">
+      <c r="E429" s="8">
         <v>-252</v>
       </c>
-      <c r="F429" s="35">
+      <c r="F429" s="8">
         <v>44224</v>
       </c>
     </row>
@@ -10643,16 +10634,16 @@
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="38" t="s">
+      <c r="C430" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="35">
+      <c r="D430" s="8">
         <v>99689</v>
       </c>
-      <c r="E430" s="35">
+      <c r="E430" s="8">
         <v>1383</v>
       </c>
-      <c r="F430" s="35">
+      <c r="F430" s="8">
         <v>101072</v>
       </c>
     </row>
@@ -10663,16 +10654,16 @@
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="38" t="s">
+      <c r="C431" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="35">
+      <c r="D431" s="8">
         <v>83530</v>
       </c>
-      <c r="E431" s="35">
+      <c r="E431" s="8">
         <v>2259</v>
       </c>
-      <c r="F431" s="35">
+      <c r="F431" s="8">
         <v>85789</v>
       </c>
     </row>
@@ -10683,17 +10674,17 @@
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="38" t="s">
+      <c r="C432" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="35">
+      <c r="D432" s="8">
         <v>59752</v>
       </c>
-      <c r="E432" s="35">
-        <v>703</v>
-      </c>
-      <c r="F432" s="35">
-        <v>60455</v>
+      <c r="E432" s="8">
+        <v>711</v>
+      </c>
+      <c r="F432" s="8">
+        <v>60463</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -10703,17 +10694,17 @@
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="38" t="s">
+      <c r="C433" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="35">
+      <c r="D433" s="8">
         <v>40427</v>
       </c>
-      <c r="E433" s="35">
-        <v>0</v>
-      </c>
-      <c r="F433" s="35">
-        <v>40427</v>
+      <c r="E433" s="8">
+        <v>-85</v>
+      </c>
+      <c r="F433" s="8">
+        <v>40342</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -10723,16 +10714,16 @@
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="38" t="s">
+      <c r="C434" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="35">
+      <c r="D434" s="8">
         <v>36123</v>
       </c>
-      <c r="E434" s="35">
-        <v>0</v>
-      </c>
-      <c r="F434" s="35">
+      <c r="E434" s="8">
+        <v>0</v>
+      </c>
+      <c r="F434" s="8">
         <v>36123</v>
       </c>
     </row>
@@ -10743,16 +10734,16 @@
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="38" t="s">
+      <c r="C435" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="35">
+      <c r="D435" s="8">
         <v>28792</v>
       </c>
-      <c r="E435" s="35">
-        <v>0</v>
-      </c>
-      <c r="F435" s="35">
+      <c r="E435" s="8">
+        <v>0</v>
+      </c>
+      <c r="F435" s="8">
         <v>28792</v>
       </c>
     </row>
@@ -10763,17 +10754,17 @@
       <c r="B436" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="38" t="s">
+      <c r="C436" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="35">
+      <c r="D436" s="8">
         <v>10316</v>
       </c>
-      <c r="E436" s="35">
-        <v>1198</v>
-      </c>
-      <c r="F436" s="35">
-        <v>11514</v>
+      <c r="E436" s="8">
+        <v>1231</v>
+      </c>
+      <c r="F436" s="8">
+        <v>11547</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -10783,17 +10774,37 @@
       <c r="B437" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C437" s="39" t="s">
+      <c r="C437" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="D437" s="36">
+      <c r="D437" s="8">
         <v>12812</v>
       </c>
-      <c r="E437" s="36">
-        <v>0</v>
-      </c>
-      <c r="F437" s="36">
+      <c r="E437" s="8">
+        <v>0</v>
+      </c>
+      <c r="F437" s="8">
         <v>12812</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A438" s="18">
+        <v>19</v>
+      </c>
+      <c r="B438" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D438" s="1">
+        <v>11333</v>
+      </c>
+      <c r="E438" s="1">
+        <v>0</v>
+      </c>
+      <c r="F438" s="1">
+        <v>11333</v>
       </c>
     </row>
   </sheetData>
@@ -10804,7 +10815,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L437"/>
+  <dimension ref="A1:L438"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19246,16 +19257,16 @@
       <c r="B419" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C419" s="40" t="s">
+      <c r="C419" s="34" t="s">
         <v>444</v>
       </c>
-      <c r="D419" s="41">
+      <c r="D419" s="35">
         <v>3477</v>
       </c>
-      <c r="E419" s="41">
+      <c r="E419" s="35">
         <v>763</v>
       </c>
-      <c r="F419" s="41">
+      <c r="F419" s="35">
         <v>4240</v>
       </c>
     </row>
@@ -19266,7 +19277,7 @@
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="42" t="s">
+      <c r="C420" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D420" s="6">
@@ -19286,7 +19297,7 @@
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="42" t="s">
+      <c r="C421" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D421" s="8">
@@ -19306,7 +19317,7 @@
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="42" t="s">
+      <c r="C422" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D422" s="8">
@@ -19326,7 +19337,7 @@
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="42" t="s">
+      <c r="C423" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D423" s="8">
@@ -19346,7 +19357,7 @@
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="42" t="s">
+      <c r="C424" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D424" s="8">
@@ -19366,7 +19377,7 @@
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="42" t="s">
+      <c r="C425" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D425" s="8">
@@ -19386,7 +19397,7 @@
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="42" t="s">
+      <c r="C426" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D426" s="8">
@@ -19406,7 +19417,7 @@
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="42" t="s">
+      <c r="C427" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D427" s="8">
@@ -19426,7 +19437,7 @@
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="42" t="s">
+      <c r="C428" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D428" s="8">
@@ -19446,7 +19457,7 @@
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="42" t="s">
+      <c r="C429" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D429" s="8">
@@ -19466,7 +19477,7 @@
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="42" t="s">
+      <c r="C430" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D430" s="8">
@@ -19486,7 +19497,7 @@
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="42" t="s">
+      <c r="C431" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D431" s="8">
@@ -19506,7 +19517,7 @@
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="42" t="s">
+      <c r="C432" s="7" t="s">
         <v>448</v>
       </c>
       <c r="D432" s="8">
@@ -19526,7 +19537,7 @@
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="42" t="s">
+      <c r="C433" s="7" t="s">
         <v>449</v>
       </c>
       <c r="D433" s="8">
@@ -19546,7 +19557,7 @@
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="42" t="s">
+      <c r="C434" s="7" t="s">
         <v>450</v>
       </c>
       <c r="D434" s="8">
@@ -19566,7 +19577,7 @@
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="42" t="s">
+      <c r="C435" s="7" t="s">
         <v>451</v>
       </c>
       <c r="D435" s="8">
@@ -19586,17 +19597,17 @@
       <c r="B436" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="42" t="s">
+      <c r="C436" s="7" t="s">
         <v>452</v>
       </c>
       <c r="D436" s="8">
         <v>26534</v>
       </c>
       <c r="E436" s="8">
-        <v>845</v>
+        <v>2864</v>
       </c>
       <c r="F436" s="8">
-        <v>27379</v>
+        <v>29398</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -19606,17 +19617,37 @@
       <c r="B437" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C437" s="42" t="s">
+      <c r="C437" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="D437" s="1">
+      <c r="D437" s="8">
         <v>19714</v>
       </c>
-      <c r="E437" s="1">
-        <v>0</v>
-      </c>
-      <c r="F437" s="1">
-        <v>19714</v>
+      <c r="E437" s="8">
+        <v>604</v>
+      </c>
+      <c r="F437" s="8">
+        <v>20318</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A438" s="3">
+        <v>19</v>
+      </c>
+      <c r="B438" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D438" s="1">
+        <v>15115</v>
+      </c>
+      <c r="E438" s="1">
+        <v>0</v>
+      </c>
+      <c r="F438" s="1">
+        <v>15115</v>
       </c>
     </row>
   </sheetData>
@@ -19635,17 +19666,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -19872,6 +19892,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
@@ -19881,17 +19912,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19908,4 +19928,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Myburgh Swiegers\Projects\Codex_GDI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583AF3BC-595B-4404-B96B-116C0E939D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E3DD33-2F6D-4340-987D-D28149C4A89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-28980" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="457">
   <si>
     <t>2024/25</t>
   </si>
@@ -1402,6 +1402,12 @@
   </si>
   <si>
     <t>04/07 - 10/07/2026</t>
+  </si>
+  <si>
+    <t>11/07 - 17/07/2026</t>
+  </si>
+  <si>
+    <t>18/07 - 24/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1418,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1467,6 +1473,11 @@
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1635,7 +1646,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1682,12 +1693,17 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1971,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L438"/>
+  <dimension ref="A1:L440"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -2240,7 +2256,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="13">
-        <v>910530</v>
+        <v>874805</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -10428,383 +10444,423 @@
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A420" s="30">
+      <c r="A420" s="40">
         <v>1</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="5" t="s">
+      <c r="C420" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="6">
+      <c r="D420" s="35">
         <v>8059</v>
       </c>
-      <c r="E420" s="6">
+      <c r="E420" s="35">
         <v>742</v>
       </c>
-      <c r="F420" s="6">
+      <c r="F420" s="35">
         <v>8801</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A421" s="7">
+      <c r="A421" s="36">
         <v>2</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="7" t="s">
+      <c r="C421" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="8">
+      <c r="D421" s="37">
         <v>22734</v>
       </c>
-      <c r="E421" s="8">
+      <c r="E421" s="37">
         <v>922</v>
       </c>
-      <c r="F421" s="8">
+      <c r="F421" s="37">
         <v>23656</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A422" s="7">
+      <c r="A422" s="36">
         <v>3</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="7" t="s">
+      <c r="C422" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="8">
+      <c r="D422" s="37">
         <v>26484</v>
       </c>
-      <c r="E422" s="8">
+      <c r="E422" s="37">
         <v>3923</v>
       </c>
-      <c r="F422" s="8">
+      <c r="F422" s="37">
         <v>30407</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A423" s="7">
+      <c r="A423" s="36">
         <v>4</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="7" t="s">
+      <c r="C423" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="8">
+      <c r="D423" s="37">
         <v>17047</v>
       </c>
-      <c r="E423" s="8">
+      <c r="E423" s="37">
         <v>2351</v>
       </c>
-      <c r="F423" s="8">
+      <c r="F423" s="37">
         <v>19398</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A424" s="7">
+      <c r="A424" s="36">
         <v>5</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="7" t="s">
+      <c r="C424" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="8">
+      <c r="D424" s="37">
         <v>39182</v>
       </c>
-      <c r="E424" s="8">
+      <c r="E424" s="37">
         <v>2818</v>
       </c>
-      <c r="F424" s="8">
+      <c r="F424" s="37">
         <v>42000</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A425" s="7">
+      <c r="A425" s="36">
         <v>6</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="7" t="s">
+      <c r="C425" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="8">
+      <c r="D425" s="37">
         <v>75766</v>
       </c>
-      <c r="E425" s="8">
+      <c r="E425" s="37">
         <v>3686</v>
       </c>
-      <c r="F425" s="8">
+      <c r="F425" s="37">
         <v>79452</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A426" s="7">
+      <c r="A426" s="36">
         <v>7</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="7" t="s">
+      <c r="C426" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="8">
+      <c r="D426" s="37">
         <v>56615</v>
       </c>
-      <c r="E426" s="8">
+      <c r="E426" s="37">
         <v>631</v>
       </c>
-      <c r="F426" s="8">
+      <c r="F426" s="37">
         <v>57246</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A427" s="7">
+      <c r="A427" s="36">
         <v>8</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="7" t="s">
+      <c r="C427" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="8">
+      <c r="D427" s="37">
         <v>33342</v>
       </c>
-      <c r="E427" s="8">
+      <c r="E427" s="37">
         <v>2446</v>
       </c>
-      <c r="F427" s="8">
+      <c r="F427" s="37">
         <v>35788</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A428" s="7">
+      <c r="A428" s="36">
         <v>9</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="7" t="s">
+      <c r="C428" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="8">
+      <c r="D428" s="37">
         <v>55113</v>
       </c>
-      <c r="E428" s="8">
+      <c r="E428" s="37">
         <v>1637</v>
       </c>
-      <c r="F428" s="8">
+      <c r="F428" s="37">
         <v>56750</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A429" s="7">
+      <c r="A429" s="36">
         <v>10</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="7" t="s">
+      <c r="C429" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="8">
+      <c r="D429" s="37">
         <v>44476</v>
       </c>
-      <c r="E429" s="8">
+      <c r="E429" s="37">
         <v>-252</v>
       </c>
-      <c r="F429" s="8">
+      <c r="F429" s="37">
         <v>44224</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A430" s="7">
+      <c r="A430" s="36">
         <v>11</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="7" t="s">
+      <c r="C430" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="8">
+      <c r="D430" s="37">
         <v>99689</v>
       </c>
-      <c r="E430" s="8">
+      <c r="E430" s="37">
         <v>1383</v>
       </c>
-      <c r="F430" s="8">
+      <c r="F430" s="37">
         <v>101072</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A431" s="7">
+      <c r="A431" s="36">
         <v>12</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="7" t="s">
+      <c r="C431" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="8">
+      <c r="D431" s="37">
         <v>83530</v>
       </c>
-      <c r="E431" s="8">
+      <c r="E431" s="37">
         <v>2259</v>
       </c>
-      <c r="F431" s="8">
+      <c r="F431" s="37">
         <v>85789</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A432" s="7">
+      <c r="A432" s="36">
         <v>13</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="7" t="s">
+      <c r="C432" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="8">
+      <c r="D432" s="37">
         <v>59752</v>
       </c>
-      <c r="E432" s="8">
+      <c r="E432" s="37">
         <v>711</v>
       </c>
-      <c r="F432" s="8">
+      <c r="F432" s="37">
         <v>60463</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A433" s="7">
+      <c r="A433" s="36">
         <v>14</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="7" t="s">
+      <c r="C433" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="8">
+      <c r="D433" s="37">
         <v>40427</v>
       </c>
-      <c r="E433" s="8">
-        <v>-85</v>
-      </c>
-      <c r="F433" s="8">
-        <v>40342</v>
+      <c r="E433" s="37">
+        <v>304</v>
+      </c>
+      <c r="F433" s="37">
+        <v>40731</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A434" s="2">
+      <c r="A434" s="36">
         <v>15</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="7" t="s">
+      <c r="C434" s="36" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="8">
+      <c r="D434" s="37">
         <v>36123</v>
       </c>
-      <c r="E434" s="8">
-        <v>0</v>
-      </c>
-      <c r="F434" s="8">
-        <v>36123</v>
+      <c r="E434" s="37">
+        <v>284</v>
+      </c>
+      <c r="F434" s="37">
+        <v>36407</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A435" s="2">
+      <c r="A435" s="36">
         <v>16</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="7" t="s">
+      <c r="C435" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="8">
+      <c r="D435" s="37">
         <v>28792</v>
       </c>
-      <c r="E435" s="8">
-        <v>0</v>
-      </c>
-      <c r="F435" s="8">
-        <v>28792</v>
+      <c r="E435" s="37">
+        <v>-343</v>
+      </c>
+      <c r="F435" s="37">
+        <v>28449</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A436" s="32">
+      <c r="A436" s="36">
         <v>17</v>
       </c>
-      <c r="B436" s="33" t="s">
+      <c r="B436" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="7" t="s">
+      <c r="C436" s="36" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="8">
+      <c r="D436" s="37">
         <v>10316</v>
       </c>
-      <c r="E436" s="8">
-        <v>1231</v>
-      </c>
-      <c r="F436" s="8">
-        <v>11547</v>
+      <c r="E436" s="37">
+        <v>1294</v>
+      </c>
+      <c r="F436" s="37">
+        <v>11610</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A437" s="18">
+      <c r="A437" s="36">
         <v>18</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C437" s="7" t="s">
+      <c r="C437" s="36" t="s">
         <v>453</v>
       </c>
-      <c r="D437" s="8">
+      <c r="D437" s="37">
         <v>12812</v>
       </c>
-      <c r="E437" s="8">
-        <v>0</v>
-      </c>
-      <c r="F437" s="8">
+      <c r="E437" s="37">
+        <v>0</v>
+      </c>
+      <c r="F437" s="37">
         <v>12812</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A438" s="18">
+      <c r="A438" s="36">
         <v>19</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C438" s="2" t="s">
+      <c r="C438" s="36" t="s">
         <v>454</v>
       </c>
-      <c r="D438" s="1">
+      <c r="D438" s="37">
         <v>11333</v>
       </c>
-      <c r="E438" s="1">
-        <v>0</v>
-      </c>
-      <c r="F438" s="1">
-        <v>11333</v>
+      <c r="E438" s="37">
+        <v>346</v>
+      </c>
+      <c r="F438" s="37">
+        <v>11679</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A439" s="36">
+        <v>20</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C439" s="36" t="s">
+        <v>455</v>
+      </c>
+      <c r="D439" s="37">
+        <v>8619</v>
+      </c>
+      <c r="E439" s="37">
+        <v>283</v>
+      </c>
+      <c r="F439" s="37">
+        <v>8902</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A440" s="38">
+        <v>21</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C440" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="D440" s="39">
+        <v>7083</v>
+      </c>
+      <c r="E440" s="39">
+        <v>0</v>
+      </c>
+      <c r="F440" s="39">
+        <v>7083</v>
       </c>
     </row>
   </sheetData>
@@ -10815,7 +10871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L438"/>
+  <dimension ref="A1:L440"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19251,22 +19307,22 @@
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A419" s="31">
+      <c r="A419" s="30">
         <v>52</v>
       </c>
-      <c r="B419" s="31" t="s">
+      <c r="B419" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C419" s="34" t="s">
+      <c r="C419" s="32" t="s">
         <v>444</v>
       </c>
-      <c r="D419" s="35">
+      <c r="D419" s="33">
         <v>3477</v>
       </c>
-      <c r="E419" s="35">
+      <c r="E419" s="33">
         <v>763</v>
       </c>
-      <c r="F419" s="35">
+      <c r="F419" s="33">
         <v>4240</v>
       </c>
     </row>
@@ -19504,10 +19560,10 @@
         <v>561432</v>
       </c>
       <c r="E431" s="8">
-        <v>9166</v>
+        <v>9095</v>
       </c>
       <c r="F431" s="8">
-        <v>570598</v>
+        <v>570527</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -19524,10 +19580,10 @@
         <v>370449</v>
       </c>
       <c r="E432" s="8">
-        <v>25159</v>
+        <v>25426</v>
       </c>
       <c r="F432" s="8">
-        <v>395608</v>
+        <v>395875</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -19544,10 +19600,10 @@
         <v>189233</v>
       </c>
       <c r="E433" s="8">
-        <v>4432</v>
+        <v>8006</v>
       </c>
       <c r="F433" s="8">
-        <v>193665</v>
+        <v>197239</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -19564,10 +19620,10 @@
         <v>96365</v>
       </c>
       <c r="E434" s="8">
-        <v>0</v>
+        <v>2837</v>
       </c>
       <c r="F434" s="8">
-        <v>96365</v>
+        <v>99202</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -19584,10 +19640,10 @@
         <v>62064</v>
       </c>
       <c r="E435" s="8">
-        <v>0</v>
+        <v>-1366</v>
       </c>
       <c r="F435" s="8">
-        <v>62064</v>
+        <v>60698</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -19604,10 +19660,10 @@
         <v>26534</v>
       </c>
       <c r="E436" s="8">
-        <v>2864</v>
+        <v>5983</v>
       </c>
       <c r="F436" s="8">
-        <v>29398</v>
+        <v>32517</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -19624,10 +19680,10 @@
         <v>19714</v>
       </c>
       <c r="E437" s="8">
-        <v>604</v>
+        <v>676</v>
       </c>
       <c r="F437" s="8">
-        <v>20318</v>
+        <v>20390</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -19637,17 +19693,57 @@
       <c r="B438" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C438" s="2" t="s">
+      <c r="C438" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="D438" s="1">
+      <c r="D438" s="8">
         <v>15115</v>
       </c>
-      <c r="E438" s="1">
-        <v>0</v>
-      </c>
-      <c r="F438" s="1">
-        <v>15115</v>
+      <c r="E438" s="8">
+        <v>981</v>
+      </c>
+      <c r="F438" s="8">
+        <v>16096</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A439" s="3">
+        <v>20</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C439" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="D439" s="8">
+        <v>14395</v>
+      </c>
+      <c r="E439" s="8">
+        <v>500</v>
+      </c>
+      <c r="F439" s="8">
+        <v>14895</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A440" s="3">
+        <v>21</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D440" s="1">
+        <v>9792</v>
+      </c>
+      <c r="E440" s="1">
+        <v>0</v>
+      </c>
+      <c r="F440" s="1">
+        <v>9792</v>
       </c>
     </row>
   </sheetData>
@@ -19666,6 +19762,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -19892,17 +19999,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
@@ -19912,6 +20008,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19928,15 +20035,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E3DD33-2F6D-4340-987D-D28149C4A89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A48BDC-9CE0-4828-B4B5-897B482A5CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28980" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="458">
   <si>
     <t>2024/25</t>
   </si>
@@ -1408,6 +1408,9 @@
   </si>
   <si>
     <t>18/07 - 24/07/2026</t>
+  </si>
+  <si>
+    <t>25/07 - 31/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1649,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1697,12 +1700,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -1987,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L440"/>
+  <dimension ref="A1:L441"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10444,423 +10443,443 @@
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A420" s="40">
+      <c r="A420" s="36">
         <v>1</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="34" t="s">
+      <c r="C420" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="35">
+      <c r="D420" s="6">
         <v>8059</v>
       </c>
-      <c r="E420" s="35">
+      <c r="E420" s="6">
         <v>742</v>
       </c>
-      <c r="F420" s="35">
+      <c r="F420" s="6">
         <v>8801</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A421" s="36">
+      <c r="A421" s="34">
         <v>2</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="36" t="s">
+      <c r="C421" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="37">
+      <c r="D421" s="8">
         <v>22734</v>
       </c>
-      <c r="E421" s="37">
+      <c r="E421" s="8">
         <v>922</v>
       </c>
-      <c r="F421" s="37">
+      <c r="F421" s="8">
         <v>23656</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A422" s="36">
+      <c r="A422" s="34">
         <v>3</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="36" t="s">
+      <c r="C422" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="37">
+      <c r="D422" s="8">
         <v>26484</v>
       </c>
-      <c r="E422" s="37">
+      <c r="E422" s="8">
         <v>3923</v>
       </c>
-      <c r="F422" s="37">
+      <c r="F422" s="8">
         <v>30407</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A423" s="36">
+      <c r="A423" s="34">
         <v>4</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="36" t="s">
+      <c r="C423" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="37">
+      <c r="D423" s="8">
         <v>17047</v>
       </c>
-      <c r="E423" s="37">
+      <c r="E423" s="8">
         <v>2351</v>
       </c>
-      <c r="F423" s="37">
+      <c r="F423" s="8">
         <v>19398</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A424" s="36">
+      <c r="A424" s="34">
         <v>5</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="36" t="s">
+      <c r="C424" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="37">
+      <c r="D424" s="8">
         <v>39182</v>
       </c>
-      <c r="E424" s="37">
+      <c r="E424" s="8">
         <v>2818</v>
       </c>
-      <c r="F424" s="37">
+      <c r="F424" s="8">
         <v>42000</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A425" s="36">
+      <c r="A425" s="34">
         <v>6</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="36" t="s">
+      <c r="C425" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="37">
+      <c r="D425" s="8">
         <v>75766</v>
       </c>
-      <c r="E425" s="37">
+      <c r="E425" s="8">
         <v>3686</v>
       </c>
-      <c r="F425" s="37">
+      <c r="F425" s="8">
         <v>79452</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A426" s="36">
+      <c r="A426" s="34">
         <v>7</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="36" t="s">
+      <c r="C426" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="37">
+      <c r="D426" s="8">
         <v>56615</v>
       </c>
-      <c r="E426" s="37">
-        <v>631</v>
-      </c>
-      <c r="F426" s="37">
-        <v>57246</v>
+      <c r="E426" s="8">
+        <v>651</v>
+      </c>
+      <c r="F426" s="8">
+        <v>57266</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A427" s="36">
+      <c r="A427" s="34">
         <v>8</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="36" t="s">
+      <c r="C427" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="37">
+      <c r="D427" s="8">
         <v>33342</v>
       </c>
-      <c r="E427" s="37">
+      <c r="E427" s="8">
         <v>2446</v>
       </c>
-      <c r="F427" s="37">
+      <c r="F427" s="8">
         <v>35788</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A428" s="36">
+      <c r="A428" s="34">
         <v>9</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="36" t="s">
+      <c r="C428" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="37">
+      <c r="D428" s="8">
         <v>55113</v>
       </c>
-      <c r="E428" s="37">
+      <c r="E428" s="8">
         <v>1637</v>
       </c>
-      <c r="F428" s="37">
+      <c r="F428" s="8">
         <v>56750</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A429" s="36">
+      <c r="A429" s="34">
         <v>10</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="36" t="s">
+      <c r="C429" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="37">
+      <c r="D429" s="8">
         <v>44476</v>
       </c>
-      <c r="E429" s="37">
+      <c r="E429" s="8">
         <v>-252</v>
       </c>
-      <c r="F429" s="37">
+      <c r="F429" s="8">
         <v>44224</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A430" s="36">
+      <c r="A430" s="34">
         <v>11</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="36" t="s">
+      <c r="C430" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="37">
+      <c r="D430" s="8">
         <v>99689</v>
       </c>
-      <c r="E430" s="37">
+      <c r="E430" s="8">
         <v>1383</v>
       </c>
-      <c r="F430" s="37">
+      <c r="F430" s="8">
         <v>101072</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A431" s="36">
+      <c r="A431" s="34">
         <v>12</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="36" t="s">
+      <c r="C431" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="37">
+      <c r="D431" s="8">
         <v>83530</v>
       </c>
-      <c r="E431" s="37">
+      <c r="E431" s="8">
         <v>2259</v>
       </c>
-      <c r="F431" s="37">
+      <c r="F431" s="8">
         <v>85789</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A432" s="36">
+      <c r="A432" s="34">
         <v>13</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="36" t="s">
+      <c r="C432" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="37">
+      <c r="D432" s="8">
         <v>59752</v>
       </c>
-      <c r="E432" s="37">
+      <c r="E432" s="8">
         <v>711</v>
       </c>
-      <c r="F432" s="37">
+      <c r="F432" s="8">
         <v>60463</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A433" s="36">
+      <c r="A433" s="34">
         <v>14</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="36" t="s">
+      <c r="C433" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="37">
+      <c r="D433" s="8">
         <v>40427</v>
       </c>
-      <c r="E433" s="37">
+      <c r="E433" s="8">
         <v>304</v>
       </c>
-      <c r="F433" s="37">
+      <c r="F433" s="8">
         <v>40731</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A434" s="36">
+      <c r="A434" s="34">
         <v>15</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="36" t="s">
+      <c r="C434" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="37">
+      <c r="D434" s="8">
         <v>36123</v>
       </c>
-      <c r="E434" s="37">
-        <v>284</v>
-      </c>
-      <c r="F434" s="37">
-        <v>36407</v>
+      <c r="E434" s="8">
+        <v>315</v>
+      </c>
+      <c r="F434" s="8">
+        <v>36438</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A435" s="36">
+      <c r="A435" s="34">
         <v>16</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="36" t="s">
+      <c r="C435" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="37">
+      <c r="D435" s="8">
         <v>28792</v>
       </c>
-      <c r="E435" s="37">
+      <c r="E435" s="8">
         <v>-343</v>
       </c>
-      <c r="F435" s="37">
+      <c r="F435" s="8">
         <v>28449</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A436" s="36">
+      <c r="A436" s="34">
         <v>17</v>
       </c>
       <c r="B436" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="36" t="s">
+      <c r="C436" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="37">
+      <c r="D436" s="8">
         <v>10316</v>
       </c>
-      <c r="E436" s="37">
+      <c r="E436" s="8">
         <v>1294</v>
       </c>
-      <c r="F436" s="37">
+      <c r="F436" s="8">
         <v>11610</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A437" s="36">
+      <c r="A437" s="34">
         <v>18</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C437" s="36" t="s">
+      <c r="C437" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="D437" s="37">
+      <c r="D437" s="8">
         <v>12812</v>
       </c>
-      <c r="E437" s="37">
-        <v>0</v>
-      </c>
-      <c r="F437" s="37">
+      <c r="E437" s="8">
+        <v>0</v>
+      </c>
+      <c r="F437" s="8">
         <v>12812</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A438" s="36">
+      <c r="A438" s="34">
         <v>19</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C438" s="36" t="s">
+      <c r="C438" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="D438" s="37">
+      <c r="D438" s="8">
         <v>11333</v>
       </c>
-      <c r="E438" s="37">
+      <c r="E438" s="8">
         <v>346</v>
       </c>
-      <c r="F438" s="37">
+      <c r="F438" s="8">
         <v>11679</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A439" s="36">
+      <c r="A439" s="34">
         <v>20</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C439" s="36" t="s">
+      <c r="C439" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D439" s="37">
+      <c r="D439" s="8">
         <v>8619</v>
       </c>
-      <c r="E439" s="37">
+      <c r="E439" s="8">
         <v>283</v>
       </c>
-      <c r="F439" s="37">
+      <c r="F439" s="8">
         <v>8902</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A440" s="38">
+      <c r="A440" s="35">
         <v>21</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C440" s="38" t="s">
+      <c r="C440" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D440" s="39">
+      <c r="D440" s="8">
         <v>7083</v>
       </c>
-      <c r="E440" s="39">
-        <v>0</v>
-      </c>
-      <c r="F440" s="39">
+      <c r="E440" s="8">
+        <v>0</v>
+      </c>
+      <c r="F440" s="8">
         <v>7083</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A441" s="35">
+        <v>22</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D441" s="1">
+        <v>5251</v>
+      </c>
+      <c r="E441" s="1">
+        <v>0</v>
+      </c>
+      <c r="F441" s="1">
+        <v>5251</v>
       </c>
     </row>
   </sheetData>
@@ -10871,7 +10890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L440"/>
+  <dimension ref="A1:L441"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19733,17 +19752,37 @@
       <c r="B440" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C440" s="2" t="s">
+      <c r="C440" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D440" s="1">
+      <c r="D440" s="8">
         <v>9792</v>
       </c>
-      <c r="E440" s="1">
-        <v>0</v>
-      </c>
-      <c r="F440" s="1">
+      <c r="E440" s="8">
+        <v>0</v>
+      </c>
+      <c r="F440" s="8">
         <v>9792</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A441" s="3">
+        <v>22</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D441" s="1">
+        <v>5680</v>
+      </c>
+      <c r="E441" s="1">
+        <v>0</v>
+      </c>
+      <c r="F441" s="1">
+        <v>5680</v>
       </c>
     </row>
   </sheetData>
@@ -19762,17 +19801,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -19999,6 +20027,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
@@ -20008,17 +20047,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20035,4 +20063,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A48BDC-9CE0-4828-B4B5-897B482A5CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03269F05-2CF7-49A8-BD37-B7333F6D8D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="459">
   <si>
     <t>2024/25</t>
   </si>
@@ -1411,6 +1411,9 @@
   </si>
   <si>
     <t>25/07 - 31/07/2026</t>
+  </si>
+  <si>
+    <t>01/08 - 07/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1652,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1703,6 +1706,10 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1986,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L441"/>
+  <dimension ref="A1:L442"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10449,16 +10456,16 @@
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="5" t="s">
+      <c r="C420" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="6">
+      <c r="D420" s="38">
         <v>8059</v>
       </c>
-      <c r="E420" s="6">
+      <c r="E420" s="38">
         <v>742</v>
       </c>
-      <c r="F420" s="6">
+      <c r="F420" s="38">
         <v>8801</v>
       </c>
     </row>
@@ -10469,16 +10476,16 @@
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="7" t="s">
+      <c r="C421" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="8">
+      <c r="D421" s="39">
         <v>22734</v>
       </c>
-      <c r="E421" s="8">
+      <c r="E421" s="39">
         <v>922</v>
       </c>
-      <c r="F421" s="8">
+      <c r="F421" s="39">
         <v>23656</v>
       </c>
     </row>
@@ -10489,16 +10496,16 @@
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="7" t="s">
+      <c r="C422" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="8">
+      <c r="D422" s="39">
         <v>26484</v>
       </c>
-      <c r="E422" s="8">
+      <c r="E422" s="39">
         <v>3923</v>
       </c>
-      <c r="F422" s="8">
+      <c r="F422" s="39">
         <v>30407</v>
       </c>
     </row>
@@ -10509,16 +10516,16 @@
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="7" t="s">
+      <c r="C423" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="8">
+      <c r="D423" s="39">
         <v>17047</v>
       </c>
-      <c r="E423" s="8">
+      <c r="E423" s="39">
         <v>2351</v>
       </c>
-      <c r="F423" s="8">
+      <c r="F423" s="39">
         <v>19398</v>
       </c>
     </row>
@@ -10529,16 +10536,16 @@
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="7" t="s">
+      <c r="C424" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="8">
+      <c r="D424" s="39">
         <v>39182</v>
       </c>
-      <c r="E424" s="8">
+      <c r="E424" s="39">
         <v>2818</v>
       </c>
-      <c r="F424" s="8">
+      <c r="F424" s="39">
         <v>42000</v>
       </c>
     </row>
@@ -10549,16 +10556,16 @@
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="7" t="s">
+      <c r="C425" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="8">
+      <c r="D425" s="39">
         <v>75766</v>
       </c>
-      <c r="E425" s="8">
+      <c r="E425" s="39">
         <v>3686</v>
       </c>
-      <c r="F425" s="8">
+      <c r="F425" s="39">
         <v>79452</v>
       </c>
     </row>
@@ -10569,16 +10576,16 @@
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="7" t="s">
+      <c r="C426" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="8">
+      <c r="D426" s="39">
         <v>56615</v>
       </c>
-      <c r="E426" s="8">
+      <c r="E426" s="39">
         <v>651</v>
       </c>
-      <c r="F426" s="8">
+      <c r="F426" s="39">
         <v>57266</v>
       </c>
     </row>
@@ -10589,16 +10596,16 @@
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="7" t="s">
+      <c r="C427" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="8">
+      <c r="D427" s="39">
         <v>33342</v>
       </c>
-      <c r="E427" s="8">
+      <c r="E427" s="39">
         <v>2446</v>
       </c>
-      <c r="F427" s="8">
+      <c r="F427" s="39">
         <v>35788</v>
       </c>
     </row>
@@ -10609,16 +10616,16 @@
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="7" t="s">
+      <c r="C428" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="8">
+      <c r="D428" s="39">
         <v>55113</v>
       </c>
-      <c r="E428" s="8">
+      <c r="E428" s="39">
         <v>1637</v>
       </c>
-      <c r="F428" s="8">
+      <c r="F428" s="39">
         <v>56750</v>
       </c>
     </row>
@@ -10629,16 +10636,16 @@
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="7" t="s">
+      <c r="C429" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="8">
+      <c r="D429" s="39">
         <v>44476</v>
       </c>
-      <c r="E429" s="8">
+      <c r="E429" s="39">
         <v>-252</v>
       </c>
-      <c r="F429" s="8">
+      <c r="F429" s="39">
         <v>44224</v>
       </c>
     </row>
@@ -10649,16 +10656,16 @@
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="7" t="s">
+      <c r="C430" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="8">
+      <c r="D430" s="39">
         <v>99689</v>
       </c>
-      <c r="E430" s="8">
+      <c r="E430" s="39">
         <v>1383</v>
       </c>
-      <c r="F430" s="8">
+      <c r="F430" s="39">
         <v>101072</v>
       </c>
     </row>
@@ -10669,16 +10676,16 @@
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="7" t="s">
+      <c r="C431" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="8">
+      <c r="D431" s="39">
         <v>83530</v>
       </c>
-      <c r="E431" s="8">
+      <c r="E431" s="39">
         <v>2259</v>
       </c>
-      <c r="F431" s="8">
+      <c r="F431" s="39">
         <v>85789</v>
       </c>
     </row>
@@ -10689,16 +10696,16 @@
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="7" t="s">
+      <c r="C432" s="34" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="8">
+      <c r="D432" s="39">
         <v>59752</v>
       </c>
-      <c r="E432" s="8">
+      <c r="E432" s="39">
         <v>711</v>
       </c>
-      <c r="F432" s="8">
+      <c r="F432" s="39">
         <v>60463</v>
       </c>
     </row>
@@ -10709,16 +10716,16 @@
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="7" t="s">
+      <c r="C433" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="8">
+      <c r="D433" s="39">
         <v>40427</v>
       </c>
-      <c r="E433" s="8">
+      <c r="E433" s="39">
         <v>304</v>
       </c>
-      <c r="F433" s="8">
+      <c r="F433" s="39">
         <v>40731</v>
       </c>
     </row>
@@ -10729,16 +10736,16 @@
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="7" t="s">
+      <c r="C434" s="34" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="8">
+      <c r="D434" s="39">
         <v>36123</v>
       </c>
-      <c r="E434" s="8">
+      <c r="E434" s="39">
         <v>315</v>
       </c>
-      <c r="F434" s="8">
+      <c r="F434" s="39">
         <v>36438</v>
       </c>
     </row>
@@ -10749,16 +10756,16 @@
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="7" t="s">
+      <c r="C435" s="34" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="8">
+      <c r="D435" s="39">
         <v>28792</v>
       </c>
-      <c r="E435" s="8">
+      <c r="E435" s="39">
         <v>-343</v>
       </c>
-      <c r="F435" s="8">
+      <c r="F435" s="39">
         <v>28449</v>
       </c>
     </row>
@@ -10769,17 +10776,17 @@
       <c r="B436" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="7" t="s">
+      <c r="C436" s="34" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="8">
+      <c r="D436" s="39">
         <v>10316</v>
       </c>
-      <c r="E436" s="8">
-        <v>1294</v>
-      </c>
-      <c r="F436" s="8">
-        <v>11610</v>
+      <c r="E436" s="39">
+        <v>1451</v>
+      </c>
+      <c r="F436" s="39">
+        <v>11767</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -10789,16 +10796,16 @@
       <c r="B437" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C437" s="7" t="s">
+      <c r="C437" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="D437" s="8">
+      <c r="D437" s="39">
         <v>12812</v>
       </c>
-      <c r="E437" s="8">
-        <v>0</v>
-      </c>
-      <c r="F437" s="8">
+      <c r="E437" s="39">
+        <v>0</v>
+      </c>
+      <c r="F437" s="39">
         <v>12812</v>
       </c>
     </row>
@@ -10809,16 +10816,16 @@
       <c r="B438" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C438" s="7" t="s">
+      <c r="C438" s="34" t="s">
         <v>454</v>
       </c>
-      <c r="D438" s="8">
+      <c r="D438" s="39">
         <v>11333</v>
       </c>
-      <c r="E438" s="8">
+      <c r="E438" s="39">
         <v>346</v>
       </c>
-      <c r="F438" s="8">
+      <c r="F438" s="39">
         <v>11679</v>
       </c>
     </row>
@@ -10829,16 +10836,16 @@
       <c r="B439" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C439" s="7" t="s">
+      <c r="C439" s="34" t="s">
         <v>455</v>
       </c>
-      <c r="D439" s="8">
+      <c r="D439" s="39">
         <v>8619</v>
       </c>
-      <c r="E439" s="8">
+      <c r="E439" s="39">
         <v>283</v>
       </c>
-      <c r="F439" s="8">
+      <c r="F439" s="39">
         <v>8902</v>
       </c>
     </row>
@@ -10849,17 +10856,17 @@
       <c r="B440" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C440" s="7" t="s">
+      <c r="C440" s="34" t="s">
         <v>456</v>
       </c>
-      <c r="D440" s="8">
+      <c r="D440" s="39">
         <v>7083</v>
       </c>
-      <c r="E440" s="8">
-        <v>0</v>
-      </c>
-      <c r="F440" s="8">
-        <v>7083</v>
+      <c r="E440" s="39">
+        <v>333</v>
+      </c>
+      <c r="F440" s="39">
+        <v>7416</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -10869,17 +10876,37 @@
       <c r="B441" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C441" s="2" t="s">
+      <c r="C441" s="34" t="s">
         <v>457</v>
       </c>
-      <c r="D441" s="1">
+      <c r="D441" s="39">
         <v>5251</v>
       </c>
-      <c r="E441" s="1">
-        <v>0</v>
-      </c>
-      <c r="F441" s="1">
-        <v>5251</v>
+      <c r="E441" s="39">
+        <v>143</v>
+      </c>
+      <c r="F441" s="39">
+        <v>5394</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A442" s="35">
+        <v>23</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C442" s="35" t="s">
+        <v>458</v>
+      </c>
+      <c r="D442" s="40">
+        <v>4703</v>
+      </c>
+      <c r="E442" s="40">
+        <v>0</v>
+      </c>
+      <c r="F442" s="40">
+        <v>4703</v>
       </c>
     </row>
   </sheetData>
@@ -10890,7 +10917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L441"/>
+  <dimension ref="A1:L442"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19759,10 +19786,10 @@
         <v>9792</v>
       </c>
       <c r="E440" s="8">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="F440" s="8">
-        <v>9792</v>
+        <v>10008</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -19772,17 +19799,37 @@
       <c r="B441" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C441" s="2" t="s">
+      <c r="C441" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="D441" s="1">
+      <c r="D441" s="8">
         <v>5680</v>
       </c>
-      <c r="E441" s="1">
-        <v>0</v>
-      </c>
-      <c r="F441" s="1">
-        <v>5680</v>
+      <c r="E441" s="8">
+        <v>2038</v>
+      </c>
+      <c r="F441" s="8">
+        <v>7718</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A442" s="3">
+        <v>23</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D442" s="1">
+        <v>5926</v>
+      </c>
+      <c r="E442" s="1">
+        <v>0</v>
+      </c>
+      <c r="F442" s="1">
+        <v>5926</v>
       </c>
     </row>
   </sheetData>
@@ -19801,6 +19848,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -20027,17 +20085,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
@@ -20047,6 +20094,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20063,15 +20121,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03269F05-2CF7-49A8-BD37-B7333F6D8D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E00838-A5D8-4C1E-B0AA-EBEE6506DA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-120" yWindow="-16335" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="460">
   <si>
     <t>2024/25</t>
   </si>
@@ -1414,6 +1414,9 @@
   </si>
   <si>
     <t>01/08 - 07/08/2026</t>
+  </si>
+  <si>
+    <t>08/08 - 14/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1655,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1706,10 +1709,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1993,7 +1992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L442"/>
+  <dimension ref="A1:L443"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10456,16 +10455,16 @@
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="37" t="s">
+      <c r="C420" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="38">
+      <c r="D420" s="6">
         <v>8059</v>
       </c>
-      <c r="E420" s="38">
+      <c r="E420" s="6">
         <v>742</v>
       </c>
-      <c r="F420" s="38">
+      <c r="F420" s="6">
         <v>8801</v>
       </c>
     </row>
@@ -10476,16 +10475,16 @@
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="34" t="s">
+      <c r="C421" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="39">
+      <c r="D421" s="8">
         <v>22734</v>
       </c>
-      <c r="E421" s="39">
+      <c r="E421" s="8">
         <v>922</v>
       </c>
-      <c r="F421" s="39">
+      <c r="F421" s="8">
         <v>23656</v>
       </c>
     </row>
@@ -10496,16 +10495,16 @@
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="34" t="s">
+      <c r="C422" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="39">
+      <c r="D422" s="8">
         <v>26484</v>
       </c>
-      <c r="E422" s="39">
+      <c r="E422" s="8">
         <v>3923</v>
       </c>
-      <c r="F422" s="39">
+      <c r="F422" s="8">
         <v>30407</v>
       </c>
     </row>
@@ -10516,16 +10515,16 @@
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="34" t="s">
+      <c r="C423" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="39">
+      <c r="D423" s="8">
         <v>17047</v>
       </c>
-      <c r="E423" s="39">
+      <c r="E423" s="8">
         <v>2351</v>
       </c>
-      <c r="F423" s="39">
+      <c r="F423" s="8">
         <v>19398</v>
       </c>
     </row>
@@ -10536,16 +10535,16 @@
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="34" t="s">
+      <c r="C424" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="39">
+      <c r="D424" s="8">
         <v>39182</v>
       </c>
-      <c r="E424" s="39">
+      <c r="E424" s="8">
         <v>2818</v>
       </c>
-      <c r="F424" s="39">
+      <c r="F424" s="8">
         <v>42000</v>
       </c>
     </row>
@@ -10556,16 +10555,16 @@
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="34" t="s">
+      <c r="C425" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="39">
+      <c r="D425" s="8">
         <v>75766</v>
       </c>
-      <c r="E425" s="39">
+      <c r="E425" s="8">
         <v>3686</v>
       </c>
-      <c r="F425" s="39">
+      <c r="F425" s="8">
         <v>79452</v>
       </c>
     </row>
@@ -10576,16 +10575,16 @@
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="34" t="s">
+      <c r="C426" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="39">
+      <c r="D426" s="8">
         <v>56615</v>
       </c>
-      <c r="E426" s="39">
+      <c r="E426" s="8">
         <v>651</v>
       </c>
-      <c r="F426" s="39">
+      <c r="F426" s="8">
         <v>57266</v>
       </c>
     </row>
@@ -10596,16 +10595,16 @@
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="34" t="s">
+      <c r="C427" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="39">
+      <c r="D427" s="8">
         <v>33342</v>
       </c>
-      <c r="E427" s="39">
+      <c r="E427" s="8">
         <v>2446</v>
       </c>
-      <c r="F427" s="39">
+      <c r="F427" s="8">
         <v>35788</v>
       </c>
     </row>
@@ -10616,16 +10615,16 @@
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="34" t="s">
+      <c r="C428" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="39">
+      <c r="D428" s="8">
         <v>55113</v>
       </c>
-      <c r="E428" s="39">
+      <c r="E428" s="8">
         <v>1637</v>
       </c>
-      <c r="F428" s="39">
+      <c r="F428" s="8">
         <v>56750</v>
       </c>
     </row>
@@ -10636,16 +10635,16 @@
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="34" t="s">
+      <c r="C429" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="39">
+      <c r="D429" s="8">
         <v>44476</v>
       </c>
-      <c r="E429" s="39">
+      <c r="E429" s="8">
         <v>-252</v>
       </c>
-      <c r="F429" s="39">
+      <c r="F429" s="8">
         <v>44224</v>
       </c>
     </row>
@@ -10656,16 +10655,16 @@
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="34" t="s">
+      <c r="C430" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="39">
+      <c r="D430" s="8">
         <v>99689</v>
       </c>
-      <c r="E430" s="39">
+      <c r="E430" s="8">
         <v>1383</v>
       </c>
-      <c r="F430" s="39">
+      <c r="F430" s="8">
         <v>101072</v>
       </c>
     </row>
@@ -10676,16 +10675,16 @@
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="34" t="s">
+      <c r="C431" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="39">
+      <c r="D431" s="8">
         <v>83530</v>
       </c>
-      <c r="E431" s="39">
+      <c r="E431" s="8">
         <v>2259</v>
       </c>
-      <c r="F431" s="39">
+      <c r="F431" s="8">
         <v>85789</v>
       </c>
     </row>
@@ -10696,16 +10695,16 @@
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="34" t="s">
+      <c r="C432" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="39">
+      <c r="D432" s="8">
         <v>59752</v>
       </c>
-      <c r="E432" s="39">
+      <c r="E432" s="8">
         <v>711</v>
       </c>
-      <c r="F432" s="39">
+      <c r="F432" s="8">
         <v>60463</v>
       </c>
     </row>
@@ -10716,16 +10715,16 @@
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="34" t="s">
+      <c r="C433" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="39">
+      <c r="D433" s="8">
         <v>40427</v>
       </c>
-      <c r="E433" s="39">
+      <c r="E433" s="8">
         <v>304</v>
       </c>
-      <c r="F433" s="39">
+      <c r="F433" s="8">
         <v>40731</v>
       </c>
     </row>
@@ -10736,16 +10735,16 @@
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="34" t="s">
+      <c r="C434" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="39">
+      <c r="D434" s="8">
         <v>36123</v>
       </c>
-      <c r="E434" s="39">
+      <c r="E434" s="8">
         <v>315</v>
       </c>
-      <c r="F434" s="39">
+      <c r="F434" s="8">
         <v>36438</v>
       </c>
     </row>
@@ -10756,16 +10755,16 @@
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="34" t="s">
+      <c r="C435" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="39">
+      <c r="D435" s="8">
         <v>28792</v>
       </c>
-      <c r="E435" s="39">
+      <c r="E435" s="8">
         <v>-343</v>
       </c>
-      <c r="F435" s="39">
+      <c r="F435" s="8">
         <v>28449</v>
       </c>
     </row>
@@ -10776,16 +10775,16 @@
       <c r="B436" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="34" t="s">
+      <c r="C436" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="39">
+      <c r="D436" s="8">
         <v>10316</v>
       </c>
-      <c r="E436" s="39">
+      <c r="E436" s="8">
         <v>1451</v>
       </c>
-      <c r="F436" s="39">
+      <c r="F436" s="8">
         <v>11767</v>
       </c>
     </row>
@@ -10796,16 +10795,16 @@
       <c r="B437" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C437" s="34" t="s">
+      <c r="C437" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="D437" s="39">
+      <c r="D437" s="8">
         <v>12812</v>
       </c>
-      <c r="E437" s="39">
-        <v>0</v>
-      </c>
-      <c r="F437" s="39">
+      <c r="E437" s="8">
+        <v>0</v>
+      </c>
+      <c r="F437" s="8">
         <v>12812</v>
       </c>
     </row>
@@ -10816,16 +10815,16 @@
       <c r="B438" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C438" s="34" t="s">
+      <c r="C438" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="D438" s="39">
+      <c r="D438" s="8">
         <v>11333</v>
       </c>
-      <c r="E438" s="39">
+      <c r="E438" s="8">
         <v>346</v>
       </c>
-      <c r="F438" s="39">
+      <c r="F438" s="8">
         <v>11679</v>
       </c>
     </row>
@@ -10836,17 +10835,17 @@
       <c r="B439" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C439" s="34" t="s">
+      <c r="C439" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D439" s="39">
+      <c r="D439" s="8">
         <v>8619</v>
       </c>
-      <c r="E439" s="39">
-        <v>283</v>
-      </c>
-      <c r="F439" s="39">
-        <v>8902</v>
+      <c r="E439" s="8">
+        <v>264</v>
+      </c>
+      <c r="F439" s="8">
+        <v>8883</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -10856,16 +10855,16 @@
       <c r="B440" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C440" s="34" t="s">
+      <c r="C440" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D440" s="39">
+      <c r="D440" s="8">
         <v>7083</v>
       </c>
-      <c r="E440" s="39">
+      <c r="E440" s="8">
         <v>333</v>
       </c>
-      <c r="F440" s="39">
+      <c r="F440" s="8">
         <v>7416</v>
       </c>
     </row>
@@ -10876,17 +10875,17 @@
       <c r="B441" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C441" s="34" t="s">
+      <c r="C441" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="D441" s="39">
+      <c r="D441" s="8">
         <v>5251</v>
       </c>
-      <c r="E441" s="39">
-        <v>143</v>
-      </c>
-      <c r="F441" s="39">
-        <v>5394</v>
+      <c r="E441" s="8">
+        <v>107</v>
+      </c>
+      <c r="F441" s="8">
+        <v>5358</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -10896,17 +10895,37 @@
       <c r="B442" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C442" s="35" t="s">
+      <c r="C442" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="D442" s="40">
+      <c r="D442" s="8">
         <v>4703</v>
       </c>
-      <c r="E442" s="40">
-        <v>0</v>
-      </c>
-      <c r="F442" s="40">
-        <v>4703</v>
+      <c r="E442" s="8">
+        <v>389</v>
+      </c>
+      <c r="F442" s="8">
+        <v>5092</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A443" s="35">
+        <v>24</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D443" s="1">
+        <v>2674</v>
+      </c>
+      <c r="E443" s="1">
+        <v>0</v>
+      </c>
+      <c r="F443" s="1">
+        <v>2674</v>
       </c>
     </row>
   </sheetData>
@@ -10917,7 +10936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L442"/>
+  <dimension ref="A1:L443"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19726,10 +19745,10 @@
         <v>19714</v>
       </c>
       <c r="E437" s="8">
-        <v>676</v>
+        <v>1995</v>
       </c>
       <c r="F437" s="8">
-        <v>20390</v>
+        <v>21709</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -19746,10 +19765,10 @@
         <v>15115</v>
       </c>
       <c r="E438" s="8">
-        <v>981</v>
+        <v>4212</v>
       </c>
       <c r="F438" s="8">
-        <v>16096</v>
+        <v>19327</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -19766,10 +19785,10 @@
         <v>14395</v>
       </c>
       <c r="E439" s="8">
-        <v>500</v>
+        <v>-751</v>
       </c>
       <c r="F439" s="8">
-        <v>14895</v>
+        <v>13644</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -19786,10 +19805,10 @@
         <v>9792</v>
       </c>
       <c r="E440" s="8">
-        <v>216</v>
+        <v>742</v>
       </c>
       <c r="F440" s="8">
-        <v>10008</v>
+        <v>10534</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -19806,10 +19825,10 @@
         <v>5680</v>
       </c>
       <c r="E441" s="8">
-        <v>2038</v>
+        <v>1719</v>
       </c>
       <c r="F441" s="8">
-        <v>7718</v>
+        <v>7399</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -19819,17 +19838,37 @@
       <c r="B442" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C442" s="2" t="s">
+      <c r="C442" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="D442" s="1">
+      <c r="D442" s="8">
         <v>5926</v>
       </c>
-      <c r="E442" s="1">
-        <v>0</v>
-      </c>
-      <c r="F442" s="1">
-        <v>5926</v>
+      <c r="E442" s="8">
+        <v>107</v>
+      </c>
+      <c r="F442" s="8">
+        <v>6033</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A443" s="3">
+        <v>24</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D443" s="1">
+        <v>4977</v>
+      </c>
+      <c r="E443" s="1">
+        <v>0</v>
+      </c>
+      <c r="F443" s="1">
+        <v>4977</v>
       </c>
     </row>
   </sheetData>
@@ -19839,26 +19878,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -20085,10 +20104,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20105,20 +20155,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E00838-A5D8-4C1E-B0AA-EBEE6506DA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD91568-51E1-4F72-9A0C-816DEAD908E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16335" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-120" yWindow="-16335" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="461">
   <si>
     <t>2024/25</t>
   </si>
@@ -1417,6 +1417,9 @@
   </si>
   <si>
     <t>08/08 - 14/08/2026</t>
+  </si>
+  <si>
+    <t>15/08 - 21/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +1995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L443"/>
+  <dimension ref="A1:L444"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10802,10 +10805,10 @@
         <v>12812</v>
       </c>
       <c r="E437" s="8">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F437" s="8">
-        <v>12812</v>
+        <v>12792</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -10822,10 +10825,10 @@
         <v>11333</v>
       </c>
       <c r="E438" s="8">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="F438" s="8">
-        <v>11679</v>
+        <v>11696</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -10842,10 +10845,10 @@
         <v>8619</v>
       </c>
       <c r="E439" s="8">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="F439" s="8">
-        <v>8883</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -10862,10 +10865,10 @@
         <v>7083</v>
       </c>
       <c r="E440" s="8">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="F440" s="8">
-        <v>7416</v>
+        <v>7474</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -10882,10 +10885,10 @@
         <v>5251</v>
       </c>
       <c r="E441" s="8">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="F441" s="8">
-        <v>5358</v>
+        <v>5373</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -10915,17 +10918,37 @@
       <c r="B443" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C443" s="2" t="s">
+      <c r="C443" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="D443" s="1">
+      <c r="D443" s="8">
         <v>2674</v>
       </c>
-      <c r="E443" s="1">
-        <v>0</v>
-      </c>
-      <c r="F443" s="1">
+      <c r="E443" s="8">
+        <v>0</v>
+      </c>
+      <c r="F443" s="8">
         <v>2674</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A444" s="35">
+        <v>25</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D444" s="1">
+        <v>2921</v>
+      </c>
+      <c r="E444" s="1">
+        <v>0</v>
+      </c>
+      <c r="F444" s="1">
+        <v>2921</v>
       </c>
     </row>
   </sheetData>
@@ -10936,7 +10959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L443"/>
+  <dimension ref="A1:L444"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19725,10 +19748,10 @@
         <v>26534</v>
       </c>
       <c r="E436" s="8">
-        <v>5983</v>
+        <v>6250</v>
       </c>
       <c r="F436" s="8">
-        <v>32517</v>
+        <v>32784</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -19745,10 +19768,10 @@
         <v>19714</v>
       </c>
       <c r="E437" s="8">
-        <v>1995</v>
+        <v>-512</v>
       </c>
       <c r="F437" s="8">
-        <v>21709</v>
+        <v>19202</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -19765,10 +19788,10 @@
         <v>15115</v>
       </c>
       <c r="E438" s="8">
-        <v>4212</v>
+        <v>6013</v>
       </c>
       <c r="F438" s="8">
-        <v>19327</v>
+        <v>21128</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -19785,10 +19808,10 @@
         <v>14395</v>
       </c>
       <c r="E439" s="8">
-        <v>-751</v>
+        <v>-462</v>
       </c>
       <c r="F439" s="8">
-        <v>13644</v>
+        <v>13933</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -19805,10 +19828,10 @@
         <v>9792</v>
       </c>
       <c r="E440" s="8">
-        <v>742</v>
+        <v>151</v>
       </c>
       <c r="F440" s="8">
-        <v>10534</v>
+        <v>9943</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -19825,10 +19848,10 @@
         <v>5680</v>
       </c>
       <c r="E441" s="8">
-        <v>1719</v>
+        <v>5198</v>
       </c>
       <c r="F441" s="8">
-        <v>7399</v>
+        <v>10878</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -19858,17 +19881,37 @@
       <c r="B443" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C443" s="2" t="s">
+      <c r="C443" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="D443" s="1">
+      <c r="D443" s="8">
         <v>4977</v>
       </c>
-      <c r="E443" s="1">
-        <v>0</v>
-      </c>
-      <c r="F443" s="1">
+      <c r="E443" s="8">
+        <v>0</v>
+      </c>
+      <c r="F443" s="8">
         <v>4977</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A444" s="3">
+        <v>25</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D444" s="1">
+        <v>6836</v>
+      </c>
+      <c r="E444" s="1">
+        <v>0</v>
+      </c>
+      <c r="F444" s="1">
+        <v>6836</v>
       </c>
     </row>
   </sheetData>
@@ -20105,6 +20148,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
@@ -20113,15 +20165,6 @@
     <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20144,6 +20187,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20152,12 +20203,4 @@
     <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD91568-51E1-4F72-9A0C-816DEAD908E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99446DA9-8640-48C1-A2F6-0A73D95A3064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16335" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="462">
   <si>
     <t>2024/25</t>
   </si>
@@ -1420,6 +1420,9 @@
   </si>
   <si>
     <t>15/08 - 21/08/2026</t>
+  </si>
+  <si>
+    <t>22/08 - 28/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1995,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L444"/>
+  <dimension ref="A1:L445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10938,17 +10941,37 @@
       <c r="B444" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C444" s="2" t="s">
+      <c r="C444" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="D444" s="1">
+      <c r="D444" s="8">
         <v>2921</v>
       </c>
-      <c r="E444" s="1">
-        <v>0</v>
-      </c>
-      <c r="F444" s="1">
+      <c r="E444" s="8">
+        <v>0</v>
+      </c>
+      <c r="F444" s="8">
         <v>2921</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A445" s="35">
+        <v>26</v>
+      </c>
+      <c r="B445" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D445" s="1">
+        <v>2216</v>
+      </c>
+      <c r="E445" s="1">
+        <v>0</v>
+      </c>
+      <c r="F445" s="1">
+        <v>2216</v>
       </c>
     </row>
   </sheetData>
@@ -10959,7 +10982,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L444"/>
+  <dimension ref="A1:L445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -11229,7 +11252,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="13">
-        <v>3043825</v>
+        <v>3010175</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -19901,17 +19924,37 @@
       <c r="B444" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C444" s="2" t="s">
+      <c r="C444" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="D444" s="1">
+      <c r="D444" s="8">
         <v>6836</v>
       </c>
-      <c r="E444" s="1">
-        <v>0</v>
-      </c>
-      <c r="F444" s="1">
+      <c r="E444" s="8">
+        <v>0</v>
+      </c>
+      <c r="F444" s="8">
         <v>6836</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A445" s="3">
+        <v>26</v>
+      </c>
+      <c r="B445" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D445" s="1">
+        <v>5698</v>
+      </c>
+      <c r="E445" s="1">
+        <v>0</v>
+      </c>
+      <c r="F445" s="1">
+        <v>5698</v>
       </c>
     </row>
   </sheetData>
@@ -19921,6 +19964,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -20147,15 +20199,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -20168,6 +20211,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20186,14 +20237,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
